--- a/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1921,6 +1921,33 @@
       <c r="E28" s="15" t="inlineStr">
         <is>
           <t>느리게로 듣고 또박또박 따라 하면 성조(4성)가 잘 잡혀요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>수업 종료 후 AI 코칭</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>화상수업을 ‘나가기’ 로 종료하면 코칭 카드가 자동으로 떠요. → 🇰🇷 한국어 / 🇺🇸 English 토글로 원하는 언어로 볼 수 있어요. → 참여도·발화비율·칭찬 횟수 요약과 잘한 점·개선점·실천 1가지를 확인해요. → ‘전체 리포트’ 를 누르면 수업 상세 + 최근 코칭 이력(품질 점수·총평)을 볼 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>매 수업 ‘오늘의 실천 1가지’만 다음 수업에서 시도해도 발화 유도가 눈에 띄게 좋아져요.</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F289"/>
+  <dimension ref="A1:F302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5126,8 +5153,156 @@
       <c r="E289" s="33" t="n"/>
       <c r="F289" s="33" t="n"/>
     </row>
+    <row r="291" ht="26" customHeight="1">
+      <c r="A291" s="21" t="inlineStr">
+        <is>
+          <t>26  🤖 수업 종료 후 AI 코칭  —  잘한 점·개선점·오늘의 실천 1가지</t>
+        </is>
+      </c>
+      <c r="B291" s="22" t="n"/>
+      <c r="C291" s="22" t="n"/>
+      <c r="D291" s="22" t="n"/>
+      <c r="E291" s="22" t="n"/>
+      <c r="F291" s="22" t="n"/>
+    </row>
+    <row r="292" ht="42" customHeight="1">
+      <c r="A292" s="23" t="inlineStr">
+        <is>
+          <t>📖 수업을 마치고 나가면, AI가 이번 수업을 분석해 ‘잘하신 점 / 개선점 / 오늘의 실천 1가지’ 를 한국어·영어로 코칭 카드로 보여줘요. 발화 비율·참여도·칭찬 횟수 같은 실제 수업 신호를 바탕으로, 감시가 아닌 따뜻한 코칭 톤으로 도와줘요.</t>
+        </is>
+      </c>
+      <c r="B292" s="24" t="n"/>
+      <c r="C292" s="24" t="n"/>
+      <c r="D292" s="24" t="n"/>
+      <c r="E292" s="24" t="n"/>
+      <c r="F292" s="24" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B293" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="30" customHeight="1">
+      <c r="A294" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B294" s="28" t="inlineStr">
+        <is>
+          <t>화상수업을 ‘나가기’ 로 종료하면 코칭 카드가 자동으로 떠요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="30" customHeight="1">
+      <c r="A295" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B295" s="28" t="inlineStr">
+        <is>
+          <t>🇰🇷 한국어 / 🇺🇸 English 토글로 원하는 언어로 볼 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="30" customHeight="1">
+      <c r="A296" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B296" s="28" t="inlineStr">
+        <is>
+          <t>참여도·발화비율·칭찬 횟수 요약과 잘한 점·개선점·실천 1가지를 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="30" customHeight="1">
+      <c r="A297" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B297" s="28" t="inlineStr">
+        <is>
+          <t>‘전체 리포트’ 를 누르면 수업 상세 + 최근 코칭 이력(품질 점수·총평)을 볼 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="24" customHeight="1">
+      <c r="A298" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B298" s="30" t="inlineStr">
+        <is>
+          <t>원어민 강사를 위해 영어가 기본, 한국어도 함께 제공돼요.</t>
+        </is>
+      </c>
+      <c r="C298" s="31" t="n"/>
+      <c r="D298" s="31" t="n"/>
+      <c r="E298" s="31" t="n"/>
+      <c r="F298" s="31" t="n"/>
+    </row>
+    <row r="299" ht="24" customHeight="1">
+      <c r="A299" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B299" s="30" t="inlineStr">
+        <is>
+          <t>수업 품질 점수(0~100) 와 상세 총평으로 스스로 성장 포인트를 잡을 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C299" s="31" t="n"/>
+      <c r="D299" s="31" t="n"/>
+      <c r="E299" s="31" t="n"/>
+      <c r="F299" s="31" t="n"/>
+    </row>
+    <row r="300" ht="24" customHeight="1">
+      <c r="A300" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B300" s="30" t="inlineStr">
+        <is>
+          <t>AI가 잠시 느려도 양쪽 언어 기본 코칭은 항상 제공돼요.</t>
+        </is>
+      </c>
+      <c r="C300" s="31" t="n"/>
+      <c r="D300" s="31" t="n"/>
+      <c r="E300" s="31" t="n"/>
+      <c r="F300" s="31" t="n"/>
+    </row>
+    <row r="301" ht="26" customHeight="1">
+      <c r="A301" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 코칭은 강사 본인의 성장을 돕기 위한 것이에요. 관리자에게는 월 누적 요약만 전달돼요.</t>
+        </is>
+      </c>
+      <c r="B301" s="35" t="n"/>
+      <c r="C301" s="35" t="n"/>
+      <c r="D301" s="35" t="n"/>
+      <c r="E301" s="35" t="n"/>
+      <c r="F301" s="35" t="n"/>
+    </row>
+    <row r="302" ht="30" customHeight="1">
+      <c r="A302" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 매 수업 ‘오늘의 실천 1가지’만 다음 수업에서 시도해도 발화 유도가 눈에 띄게 좋아져요.</t>
+        </is>
+      </c>
+      <c r="B302" s="33" t="n"/>
+      <c r="C302" s="33" t="n"/>
+      <c r="D302" s="33" t="n"/>
+      <c r="E302" s="33" t="n"/>
+      <c r="F302" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="264">
+  <mergeCells count="276">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A66:F66"/>
@@ -5150,6 +5325,8 @@
     <mergeCell ref="A239:F239"/>
     <mergeCell ref="B223:F223"/>
     <mergeCell ref="B276:F276"/>
+    <mergeCell ref="B294:F294"/>
+    <mergeCell ref="A301:F301"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A150:F150"/>
@@ -5189,6 +5366,7 @@
     <mergeCell ref="A260:F260"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B281:F281"/>
+    <mergeCell ref="A291:F291"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B133:F133"/>
@@ -5208,6 +5386,7 @@
     <mergeCell ref="A277:F277"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B54:F54"/>
+    <mergeCell ref="A292:F292"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="B185:F185"/>
@@ -5223,6 +5402,7 @@
     <mergeCell ref="A269:F269"/>
     <mergeCell ref="A151:F151"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B293:F293"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="B98:F98"/>
@@ -5244,6 +5424,7 @@
     <mergeCell ref="B146:F146"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A176:F176"/>
+    <mergeCell ref="B295:F295"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B68:F68"/>
@@ -5260,6 +5441,7 @@
     <mergeCell ref="B216:F216"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="A162:F162"/>
+    <mergeCell ref="B296:F296"/>
     <mergeCell ref="B173:F173"/>
     <mergeCell ref="A227:F227"/>
     <mergeCell ref="B271:F271"/>
@@ -5305,6 +5487,7 @@
     <mergeCell ref="A180:F180"/>
     <mergeCell ref="B225:F225"/>
     <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B299:F299"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B191:F191"/>
@@ -5318,6 +5501,7 @@
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A270:F270"/>
     <mergeCell ref="A279:F279"/>
+    <mergeCell ref="B300:F300"/>
     <mergeCell ref="B183:F183"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="B192:F192"/>
@@ -5350,11 +5534,13 @@
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B130:F130"/>
+    <mergeCell ref="A302:F302"/>
     <mergeCell ref="A247:F247"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="B262:F262"/>
     <mergeCell ref="A219:F219"/>
+    <mergeCell ref="B297:F297"/>
     <mergeCell ref="B235:F235"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="B67:F67"/>
@@ -5375,6 +5561,7 @@
     <mergeCell ref="B283:F283"/>
     <mergeCell ref="A220:F220"/>
     <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B298:F298"/>
     <mergeCell ref="B211:F211"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="B285:F285"/>

--- a/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
@@ -1108,7 +1108,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>🌐 test.mangoi.co.kr    📞 1588-0000    ✉ support@mangoi.co.kr</t>
+          <t>🌐 www.mangoi.co.kr    📞 1644-0561    ✉ support@mangoi.co.kr</t>
         </is>
       </c>
     </row>

--- a/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1948,6 +1948,114 @@
       <c r="E29" s="20" t="inlineStr">
         <is>
           <t>매 수업 ‘오늘의 실천 1가지’만 다음 수업에서 시도해도 발화 유도가 눈에 띄게 좋아져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>탭 동기화 (내 화면 그대로 학생에게)</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>평소처럼 상단 탭(칠판·동영상·학생게임·배경화면·AI웜업·복습퀴즈)을 바꿔요. → 학생 화면이 자동으로 같은 탭으로 전환되는 걸 확인해요. → 교재·파일 공유도 마찬가지로 학생에게 그대로 반영돼요.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>동영상·퀴즈로 넘어가기 전에 한마디 예고해 주면 학생이 덜 놀라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>💬</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>1:1 개별 채팅 &amp; 파일 보내기</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>하단 독의 💬 채팅을 열어요. → 받는 사람을 전체에서 학생 이름으로 바꾸면 1:1 귓속말이 돼요. → 📎 파일 버튼으로 PDF·사진·문서를 올리면 상대 화면에 다운로드 카드가 생겨요. → 받은 파일은 카드의 ⬇ 저장을 눌러 내려받아요.</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>수업 중 궁금한 걸 다른 친구 방해 없이 조용히 물어볼 때 딱 좋아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>🗓️</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>수업 연기·변경 요청하기</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>마이페이지의 수업 일정에서 해당 수업을 골라요. → 연기/변경 요청 버튼을 누르고 사유와 희망 시간을 적어요. → 제출하면 관리자 승인 후 스케줄에 자동 반영돼요. 처리 상태도 확인할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>희망 시간을 2~3개 적어주면 승인이 훨씬 빨라져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>🧾</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>내 수업료 정산 확인</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>마이페이지에서 🧾 정산 탭을 열어요. → 이번 달 수업 수·정산 금액을 확인해요. → 월을 바꿔 지난 달 내역도 조회할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>매월 초에 지난달 내역을 한 번 훑어보는 습관을 들이세요.</t>
         </is>
       </c>
     </row>
@@ -1965,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F302"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5301,284 +5409,823 @@
       <c r="E302" s="33" t="n"/>
       <c r="F302" s="33" t="n"/>
     </row>
+    <row r="304" ht="26" customHeight="1">
+      <c r="A304" s="21" t="inlineStr">
+        <is>
+          <t>27  🔄 탭 동기화 (내 화면 그대로 학생에게)  —  교사가 탭을 바꾸면 학생 화면도 함께</t>
+        </is>
+      </c>
+      <c r="B304" s="22" t="n"/>
+      <c r="C304" s="22" t="n"/>
+      <c r="D304" s="22" t="n"/>
+      <c r="E304" s="22" t="n"/>
+      <c r="F304" s="22" t="n"/>
+    </row>
+    <row r="305" ht="42" customHeight="1">
+      <c r="A305" s="23" t="inlineStr">
+        <is>
+          <t>📖 수업 중 교사가 칠판 → 동영상 → 복습퀴즈 처럼 상단 탭을 바꾸면, 학생 화면도 자동으로 같은 탭으로 넘어가요. “○○ 탭 눌러보세요”라고 말로 안내할 필요 없이, 수업 흐름을 교사가 그대로 끌고 갈 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B305" s="24" t="n"/>
+      <c r="C305" s="24" t="n"/>
+      <c r="D305" s="24" t="n"/>
+      <c r="E305" s="24" t="n"/>
+      <c r="F305" s="24" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B306" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="30" customHeight="1">
+      <c r="A307" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B307" s="28" t="inlineStr">
+        <is>
+          <t>평소처럼 상단 탭(칠판·동영상·학생게임·배경화면·AI웜업·복습퀴즈)을 바꿔요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="30" customHeight="1">
+      <c r="A308" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B308" s="28" t="inlineStr">
+        <is>
+          <t>학생 화면이 자동으로 같은 탭으로 전환되는 걸 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="30" customHeight="1">
+      <c r="A309" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B309" s="28" t="inlineStr">
+        <is>
+          <t>교재·파일 공유도 마찬가지로 학생에게 그대로 반영돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="24" customHeight="1">
+      <c r="A310" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B310" s="30" t="inlineStr">
+        <is>
+          <t>저학년 학생도 버튼을 못 찾아 헤매는 일 없이 따라와요.</t>
+        </is>
+      </c>
+      <c r="C310" s="31" t="n"/>
+      <c r="D310" s="31" t="n"/>
+      <c r="E310" s="31" t="n"/>
+      <c r="F310" s="31" t="n"/>
+    </row>
+    <row r="311" ht="24" customHeight="1">
+      <c r="A311" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B311" s="30" t="inlineStr">
+        <is>
+          <t>수업 리듬이 끊기지 않아 진행 속도가 빨라져요.</t>
+        </is>
+      </c>
+      <c r="C311" s="31" t="n"/>
+      <c r="D311" s="31" t="n"/>
+      <c r="E311" s="31" t="n"/>
+      <c r="F311" s="31" t="n"/>
+    </row>
+    <row r="312" ht="26" customHeight="1">
+      <c r="A312" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 동기화는 수업방에 함께 있는 동안 동작해요. 화면이 안 따라오면 학생에게 재입장을 안내하세요.</t>
+        </is>
+      </c>
+      <c r="B312" s="35" t="n"/>
+      <c r="C312" s="35" t="n"/>
+      <c r="D312" s="35" t="n"/>
+      <c r="E312" s="35" t="n"/>
+      <c r="F312" s="35" t="n"/>
+    </row>
+    <row r="313" ht="30" customHeight="1">
+      <c r="A313" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 동영상·퀴즈로 넘어가기 전에 한마디 예고해 주면 학생이 덜 놀라요.</t>
+        </is>
+      </c>
+      <c r="B313" s="33" t="n"/>
+      <c r="C313" s="33" t="n"/>
+      <c r="D313" s="33" t="n"/>
+      <c r="E313" s="33" t="n"/>
+      <c r="F313" s="33" t="n"/>
+    </row>
+    <row r="315" ht="26" customHeight="1">
+      <c r="A315" s="21" t="inlineStr">
+        <is>
+          <t>28  💬 1:1 개별 채팅 &amp; 파일 보내기  —  학생에게만 보이는 귓속말 + 모든 파일 공유</t>
+        </is>
+      </c>
+      <c r="B315" s="22" t="n"/>
+      <c r="C315" s="22" t="n"/>
+      <c r="D315" s="22" t="n"/>
+      <c r="E315" s="22" t="n"/>
+      <c r="F315" s="22" t="n"/>
+    </row>
+    <row r="316" ht="42" customHeight="1">
+      <c r="A316" s="23" t="inlineStr">
+        <is>
+          <t>📖 수업 채팅에 1:1 개별 채팅(DM) 이 생겼어요. 특정 학생에게만 보이는 메시지를 보낼 수 있고, PDF·이미지·문서 등 어떤 파일이든 채팅으로 공유하면 상대방 화면에 다운로드 카드로 떠요.</t>
+        </is>
+      </c>
+      <c r="B316" s="24" t="n"/>
+      <c r="C316" s="24" t="n"/>
+      <c r="D316" s="24" t="n"/>
+      <c r="E316" s="24" t="n"/>
+      <c r="F316" s="24" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B317" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="30" customHeight="1">
+      <c r="A318" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B318" s="28" t="inlineStr">
+        <is>
+          <t>하단 독의 💬 채팅을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="30" customHeight="1">
+      <c r="A319" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B319" s="28" t="inlineStr">
+        <is>
+          <t>받는 사람을 전체에서 학생 이름으로 바꾸면 1:1 귓속말이 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="30" customHeight="1">
+      <c r="A320" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B320" s="28" t="inlineStr">
+        <is>
+          <t>📎 파일 버튼으로 PDF·사진·문서를 올리면 상대 화면에 다운로드 카드가 생겨요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="30" customHeight="1">
+      <c r="A321" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B321" s="28" t="inlineStr">
+        <is>
+          <t>받은 파일은 카드의 ⬇ 저장을 눌러 내려받아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="24" customHeight="1">
+      <c r="A322" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B322" s="30" t="inlineStr">
+        <is>
+          <t>개별 채팅은 당사자끼리만 보여요.</t>
+        </is>
+      </c>
+      <c r="C322" s="31" t="n"/>
+      <c r="D322" s="31" t="n"/>
+      <c r="E322" s="31" t="n"/>
+      <c r="F322" s="31" t="n"/>
+    </row>
+    <row r="323" ht="24" customHeight="1">
+      <c r="A323" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B323" s="30" t="inlineStr">
+        <is>
+          <t>숙제 파일·오답 정리 등 수업 자료 주고받기가 한 번에 끝나요.</t>
+        </is>
+      </c>
+      <c r="C323" s="31" t="n"/>
+      <c r="D323" s="31" t="n"/>
+      <c r="E323" s="31" t="n"/>
+      <c r="F323" s="31" t="n"/>
+    </row>
+    <row r="324" ht="26" customHeight="1">
+      <c r="A324" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 개별 채팅 내용은 서버에 저장되지 않아 수업이 끝나면 사라져요. 중요한 내용은 파일로 보관하세요.</t>
+        </is>
+      </c>
+      <c r="B324" s="35" t="n"/>
+      <c r="C324" s="35" t="n"/>
+      <c r="D324" s="35" t="n"/>
+      <c r="E324" s="35" t="n"/>
+      <c r="F324" s="35" t="n"/>
+    </row>
+    <row r="325" ht="30" customHeight="1">
+      <c r="A325" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 수업 중 궁금한 걸 다른 친구 방해 없이 조용히 물어볼 때 딱 좋아요.</t>
+        </is>
+      </c>
+      <c r="B325" s="33" t="n"/>
+      <c r="C325" s="33" t="n"/>
+      <c r="D325" s="33" t="n"/>
+      <c r="E325" s="33" t="n"/>
+      <c r="F325" s="33" t="n"/>
+    </row>
+    <row r="327" ht="26" customHeight="1">
+      <c r="A327" s="21" t="inlineStr">
+        <is>
+          <t>29  🗓️ 수업 연기·변경 요청하기  —  사정이 생기면 사이트에서 바로 제출</t>
+        </is>
+      </c>
+      <c r="B327" s="22" t="n"/>
+      <c r="C327" s="22" t="n"/>
+      <c r="D327" s="22" t="n"/>
+      <c r="E327" s="22" t="n"/>
+      <c r="F327" s="22" t="n"/>
+    </row>
+    <row r="328" ht="42" customHeight="1">
+      <c r="A328" s="23" t="inlineStr">
+        <is>
+          <t>📖 갑자기 사정이 생겼을 때, 이제 사이트에서 직접 수업 연기·시간 변경을 요청할 수 있어요. 제출한 요청은 관리자에게 실시간으로 전달되고, 승인되면 스케줄에 자동 반영돼요.</t>
+        </is>
+      </c>
+      <c r="B328" s="24" t="n"/>
+      <c r="C328" s="24" t="n"/>
+      <c r="D328" s="24" t="n"/>
+      <c r="E328" s="24" t="n"/>
+      <c r="F328" s="24" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B329" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="30" customHeight="1">
+      <c r="A330" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B330" s="28" t="inlineStr">
+        <is>
+          <t>마이페이지의 수업 일정에서 해당 수업을 골라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="30" customHeight="1">
+      <c r="A331" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B331" s="28" t="inlineStr">
+        <is>
+          <t>연기/변경 요청 버튼을 누르고 사유와 희망 시간을 적어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="30" customHeight="1">
+      <c r="A332" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B332" s="28" t="inlineStr">
+        <is>
+          <t>제출하면 관리자 승인 후 스케줄에 자동 반영돼요. 처리 상태도 확인할 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="24" customHeight="1">
+      <c r="A333" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B333" s="30" t="inlineStr">
+        <is>
+          <t>전화·메신저 없이 기록이 남는 공식 요청으로 처리돼요.</t>
+        </is>
+      </c>
+      <c r="C333" s="31" t="n"/>
+      <c r="D333" s="31" t="n"/>
+      <c r="E333" s="31" t="n"/>
+      <c r="F333" s="31" t="n"/>
+    </row>
+    <row r="334" ht="24" customHeight="1">
+      <c r="A334" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B334" s="30" t="inlineStr">
+        <is>
+          <t>승인 전까지는 기존 일정이 유지되니 미리(가급적 하루 전) 요청하세요.</t>
+        </is>
+      </c>
+      <c r="C334" s="31" t="n"/>
+      <c r="D334" s="31" t="n"/>
+      <c r="E334" s="31" t="n"/>
+      <c r="F334" s="31" t="n"/>
+    </row>
+    <row r="335" ht="26" customHeight="1">
+      <c r="A335" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 임박한 변경은 학생·학부모 안내 시간이 필요해요. 급한 경우 고객센터에도 함께 알려주세요.</t>
+        </is>
+      </c>
+      <c r="B335" s="35" t="n"/>
+      <c r="C335" s="35" t="n"/>
+      <c r="D335" s="35" t="n"/>
+      <c r="E335" s="35" t="n"/>
+      <c r="F335" s="35" t="n"/>
+    </row>
+    <row r="336" ht="30" customHeight="1">
+      <c r="A336" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 희망 시간을 2~3개 적어주면 승인이 훨씬 빨라져요.</t>
+        </is>
+      </c>
+      <c r="B336" s="33" t="n"/>
+      <c r="C336" s="33" t="n"/>
+      <c r="D336" s="33" t="n"/>
+      <c r="E336" s="33" t="n"/>
+      <c r="F336" s="33" t="n"/>
+    </row>
+    <row r="338" ht="26" customHeight="1">
+      <c r="A338" s="21" t="inlineStr">
+        <is>
+          <t>30  🧾 내 수업료 정산 확인  —  이번 달 수업·정산 내역을 내가 직접</t>
+        </is>
+      </c>
+      <c r="B338" s="22" t="n"/>
+      <c r="C338" s="22" t="n"/>
+      <c r="D338" s="22" t="n"/>
+      <c r="E338" s="22" t="n"/>
+      <c r="F338" s="22" t="n"/>
+    </row>
+    <row r="339" ht="42" customHeight="1">
+      <c r="A339" s="23" t="inlineStr">
+        <is>
+          <t>📖 마이페이지의 🧾 정산 탭에서 이번 달 내 수업 횟수와 수업료 정산 내역을 직접 확인할 수 있어요. 정산 내역은 본인 것만 보이도록 보호되고, 월별로 지난 내역도 다시 볼 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B339" s="24" t="n"/>
+      <c r="C339" s="24" t="n"/>
+      <c r="D339" s="24" t="n"/>
+      <c r="E339" s="24" t="n"/>
+      <c r="F339" s="24" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B340" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="30" customHeight="1">
+      <c r="A341" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B341" s="28" t="inlineStr">
+        <is>
+          <t>마이페이지에서 🧾 정산 탭을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="30" customHeight="1">
+      <c r="A342" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B342" s="28" t="inlineStr">
+        <is>
+          <t>이번 달 수업 수·정산 금액을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="30" customHeight="1">
+      <c r="A343" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B343" s="28" t="inlineStr">
+        <is>
+          <t>월을 바꿔 지난 달 내역도 조회할 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="24" customHeight="1">
+      <c r="A344" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B344" s="30" t="inlineStr">
+        <is>
+          <t>정산 내역은 본인만 열람할 수 있어 안전해요.</t>
+        </is>
+      </c>
+      <c r="C344" s="31" t="n"/>
+      <c r="D344" s="31" t="n"/>
+      <c r="E344" s="31" t="n"/>
+      <c r="F344" s="31" t="n"/>
+    </row>
+    <row r="345" ht="24" customHeight="1">
+      <c r="A345" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B345" s="30" t="inlineStr">
+        <is>
+          <t>수업 기록과 정산이 자동으로 연결돼 누락 걱정이 없어요.</t>
+        </is>
+      </c>
+      <c r="C345" s="31" t="n"/>
+      <c r="D345" s="31" t="n"/>
+      <c r="E345" s="31" t="n"/>
+      <c r="F345" s="31" t="n"/>
+    </row>
+    <row r="346" ht="26" customHeight="1">
+      <c r="A346" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 내역이 실제와 다르면 스스로 고치지 말고 관리자(본사)에게 문의하세요.</t>
+        </is>
+      </c>
+      <c r="B346" s="35" t="n"/>
+      <c r="C346" s="35" t="n"/>
+      <c r="D346" s="35" t="n"/>
+      <c r="E346" s="35" t="n"/>
+      <c r="F346" s="35" t="n"/>
+    </row>
+    <row r="347" ht="30" customHeight="1">
+      <c r="A347" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 매월 초에 지난달 내역을 한 번 훑어보는 습관을 들이세요.</t>
+        </is>
+      </c>
+      <c r="B347" s="33" t="n"/>
+      <c r="C347" s="33" t="n"/>
+      <c r="D347" s="33" t="n"/>
+      <c r="E347" s="33" t="n"/>
+      <c r="F347" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="276">
+  <mergeCells count="317">
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B276:F276"/>
+    <mergeCell ref="B214:F214"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B253:F253"/>
+    <mergeCell ref="B342:F342"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A280:F280"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A249:F249"/>
+    <mergeCell ref="A347:F347"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A338:F338"/>
+    <mergeCell ref="A257:F257"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="A315:F315"/>
+    <mergeCell ref="B160:F160"/>
+    <mergeCell ref="B135:F135"/>
+    <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="A267:F267"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="A269:F269"/>
+    <mergeCell ref="B293:F293"/>
+    <mergeCell ref="B322:F322"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B317:F317"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B254:F254"/>
+    <mergeCell ref="B319:F319"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="A346:F346"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="B272:F272"/>
+    <mergeCell ref="B136:F136"/>
+    <mergeCell ref="B299:F299"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B243:F243"/>
+    <mergeCell ref="A270:F270"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B264:F264"/>
+    <mergeCell ref="B320:F320"/>
+    <mergeCell ref="A302:F302"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B262:F262"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A327:F327"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="A220:F220"/>
+    <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B211:F211"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="B275:F275"/>
+    <mergeCell ref="B340:F340"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B252:F252"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B234:F234"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B172:F172"/>
+    <mergeCell ref="A289:F289"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B288:F288"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A291:F291"/>
+    <mergeCell ref="B265:F265"/>
+    <mergeCell ref="A305:F305"/>
+    <mergeCell ref="A292:F292"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B125:F125"/>
+    <mergeCell ref="B185:F185"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B341:F341"/>
+    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B171:F171"/>
+    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B204:F204"/>
+    <mergeCell ref="B296:F296"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B271:F271"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B202:F202"/>
+    <mergeCell ref="B273:F273"/>
+    <mergeCell ref="A313:F313"/>
+    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A336:F336"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="B255:F255"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B284:F284"/>
+    <mergeCell ref="B222:F222"/>
+    <mergeCell ref="B344:F344"/>
+    <mergeCell ref="A339:F339"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B286:F286"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A219:F219"/>
+    <mergeCell ref="B297:F297"/>
+    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B205:F205"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="A187:F187"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="B81:F81"/>
     <mergeCell ref="B194:F194"/>
     <mergeCell ref="A118:F118"/>
-    <mergeCell ref="B252:F252"/>
     <mergeCell ref="A189:F189"/>
-    <mergeCell ref="B261:F261"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B184:F184"/>
-    <mergeCell ref="A3:F3"/>
     <mergeCell ref="B131:F131"/>
     <mergeCell ref="B236:F236"/>
-    <mergeCell ref="B214:F214"/>
-    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B307:F307"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="A239:F239"/>
     <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B276:F276"/>
     <mergeCell ref="B294:F294"/>
-    <mergeCell ref="A301:F301"/>
     <mergeCell ref="B195:F195"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="A150:F150"/>
-    <mergeCell ref="B253:F253"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B231:F231"/>
     <mergeCell ref="B287:F287"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B157:F157"/>
     <mergeCell ref="A200:F200"/>
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="B241:F241"/>
+    <mergeCell ref="A260:F260"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B242:F242"/>
+    <mergeCell ref="A335:F335"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A259:F259"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A240:F240"/>
+    <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="B333:F333"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B308:F308"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B310:F310"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="B232:F232"/>
+    <mergeCell ref="B321:F321"/>
+    <mergeCell ref="B215:F215"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B263:F263"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B323:F323"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="B244:F244"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B145:F145"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B245:F245"/>
+    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B334:F334"/>
+    <mergeCell ref="B309:F309"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="A316:F316"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B311:F311"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B329:F329"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B266:F266"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B331:F331"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B330:F330"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="B261:F261"/>
+    <mergeCell ref="B184:F184"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A301:F301"/>
+    <mergeCell ref="A239:F239"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B166:F166"/>
-    <mergeCell ref="A280:F280"/>
     <mergeCell ref="A161:F161"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B234:F234"/>
-    <mergeCell ref="A249:F249"/>
-    <mergeCell ref="A289:F289"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="A40:F40"/>
     <mergeCell ref="B168:F168"/>
-    <mergeCell ref="B288:F288"/>
-    <mergeCell ref="B84:F84"/>
     <mergeCell ref="B143:F143"/>
-    <mergeCell ref="A257:F257"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="A107:F107"/>
-    <mergeCell ref="B241:F241"/>
-    <mergeCell ref="A260:F260"/>
-    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B281:F281"/>
-    <mergeCell ref="A291:F291"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B133:F133"/>
-    <mergeCell ref="B142:F142"/>
     <mergeCell ref="B256:F256"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B213:F213"/>
     <mergeCell ref="A250:F250"/>
-    <mergeCell ref="B265:F265"/>
-    <mergeCell ref="B160:F160"/>
     <mergeCell ref="A237:F237"/>
-    <mergeCell ref="B135:F135"/>
     <mergeCell ref="A41:F41"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B233:F233"/>
-    <mergeCell ref="B242:F242"/>
     <mergeCell ref="A277:F277"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="A292:F292"/>
-    <mergeCell ref="B125:F125"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B185:F185"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A267:F267"/>
     <mergeCell ref="B121:F121"/>
-    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B167:F167"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="A269:F269"/>
-    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="B332:F332"/>
     <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B293:F293"/>
-    <mergeCell ref="B120:F120"/>
-    <mergeCell ref="A126:F126"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="A259:F259"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A240:F240"/>
-    <mergeCell ref="B17:F17"/>
     <mergeCell ref="B175:F175"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="A190:F190"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="B171:F171"/>
-    <mergeCell ref="A199:F199"/>
     <mergeCell ref="A230:F230"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B99:F99"/>
-    <mergeCell ref="A176:F176"/>
-    <mergeCell ref="B295:F295"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B83:F83"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="B254:F254"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="A304:F304"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A79:F79"/>
     <mergeCell ref="B251:F251"/>
-    <mergeCell ref="B204:F204"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B216:F216"/>
-    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B343:F343"/>
     <mergeCell ref="A162:F162"/>
-    <mergeCell ref="B296:F296"/>
-    <mergeCell ref="B173:F173"/>
     <mergeCell ref="A227:F227"/>
-    <mergeCell ref="B271:F271"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="A137:F137"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A217:F217"/>
-    <mergeCell ref="B232:F232"/>
-    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="B345:F345"/>
     <mergeCell ref="A164:F164"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B193:F193"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B295:F295"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B202:F202"/>
-    <mergeCell ref="B215:F215"/>
-    <mergeCell ref="A139:F139"/>
-    <mergeCell ref="B273:F273"/>
-    <mergeCell ref="A210:F210"/>
     <mergeCell ref="B282:F282"/>
     <mergeCell ref="A179:F179"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A129:F129"/>
-    <mergeCell ref="B263:F263"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B272:F272"/>
-    <mergeCell ref="A76:F76"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="A116:F116"/>
-    <mergeCell ref="B244:F244"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B145:F145"/>
-    <mergeCell ref="A140:F140"/>
     <mergeCell ref="A53:F53"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A324:F324"/>
     <mergeCell ref="A180:F180"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B274:F274"/>
-    <mergeCell ref="B299:F299"/>
-    <mergeCell ref="A63:F63"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B243:F243"/>
-    <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B245:F245"/>
-    <mergeCell ref="A229:F229"/>
-    <mergeCell ref="B255:F255"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="A270:F270"/>
-    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A328:F328"/>
     <mergeCell ref="B300:F300"/>
     <mergeCell ref="B183:F183"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="B192:F192"/>
     <mergeCell ref="B201:F201"/>
-    <mergeCell ref="A207:F207"/>
-    <mergeCell ref="B284:F284"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="B222:F222"/>
     <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B154:F154"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="B212:F212"/>
     <mergeCell ref="B206:F206"/>
-    <mergeCell ref="B212:F212"/>
-    <mergeCell ref="B110:F110"/>
     <mergeCell ref="B203:F203"/>
-    <mergeCell ref="B221:F221"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="B286:F286"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B155:F155"/>
-    <mergeCell ref="B264:F264"/>
-    <mergeCell ref="B102:F102"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B130:F130"/>
-    <mergeCell ref="A302:F302"/>
     <mergeCell ref="A247:F247"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B262:F262"/>
-    <mergeCell ref="A219:F219"/>
-    <mergeCell ref="B297:F297"/>
-    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="A312:F312"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B132:F132"/>
-    <mergeCell ref="A209:F209"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A52:F52"/>
     <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B103:F103"/>
     <mergeCell ref="B196:F196"/>
     <mergeCell ref="B112:F112"/>
-    <mergeCell ref="B205:F205"/>
     <mergeCell ref="B283:F283"/>
-    <mergeCell ref="A220:F220"/>
-    <mergeCell ref="B246:F246"/>
     <mergeCell ref="B298:F298"/>
-    <mergeCell ref="B211:F211"/>
-    <mergeCell ref="A148:F148"/>
     <mergeCell ref="B285:F285"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B266:F266"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B275:F275"/>
+    <mergeCell ref="A325:F325"/>
     <mergeCell ref="A119:F119"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A187:F187"/>
-    <mergeCell ref="B97:F97"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
+++ b/cloudflare-deploy/public/library/teacher/teacher-kr.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2056,168 @@
       <c r="E33" s="20" t="inlineStr">
         <is>
           <t>매월 초에 지난달 내역을 한 번 훑어보는 습관을 들이세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>🔒</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>수업 통제 3종 (집중 · 배경 잠금 · 이탈 방지)</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>수업 화면 하단 독에서 ⚙️ 설정을 열어요. → 집중 모드를 켜면 학생 화면이 수업에 고정돼요. → 배경 잠금을 켜면 학생이 배경·얼굴 꾸미기를 바꿀 수 없어요. → 이탈 방지는 켜 두면 학생이 뒤로 가기를 눌러도 정말 나갈지 한 번 물어봐요. → 수업이 끝나면 세 가지 모두 자동으로 풀립니다.</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>산만한 학생만 골라 켜는 것보다, 첫 수업부터 기본으로 켜 두는 편이 자연스럽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>✍️</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>교재 PDF — 필기 이어가기 · 빠른 페이지 이동</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>상단 탭에서 교재를 열고 PDF를 띄워요. → 필기도구로 밑줄·동그라미를 그려요. → ◀ ▶ 로 페이지를 넘기거나 페이지 번호를 직접 입력해 이동해요. → 앞 페이지로 돌아가면 아까 쓴 필기가 그대로 있어요. → 화면이 느리면 가벼운 모드를 켜세요.</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>수업 전에 자주 쓸 페이지 번호를 적어 두면 이동이 빨라집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>🔉</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>인터넷이 느릴 때 자동으로 버텨요</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>특별히 누를 것은 없어요 — 자동으로 동작합니다. → 화면이 흐려지거나 영상이 잠시 멈추면 목소리에 집중해 수업을 이어가세요. → 회선이 좋아지면 영상이 저절로 돌아옵니다. → 계속 불안정하면 학생에게 와이파이 가까이 이동을 안내해 주세요.</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>영상이 자주 끊기는 학생은 수업 전 장비 점검 화면을 한 번 돌려 보게 하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="54" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>판단력 훈련 함께하기 (수업 중)</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>수업 중 학생에게 🧠 판단력 훈련을 열게 하고 한 문제를 함께 풀어요. → 학생이 고른 보기와 적은 이유를 소리 내어 읽게 해요. → 왜 다른 보기가 덜 어울리는지 상대·말투·상황 기준으로 설명해 줘요. → 수업이 끝나면 학생 리포트에서 판단력 지수 변화를 확인해요.</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>“왜 그렇게 생각했어요?”를 영어로 묻고 한국어로 답하게 해도 좋습니다. 판단 과정이 먼저입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>🎥</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>지난 수업 녹화 다시보기</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>수업 중 상단의 REC 를 눌러 녹화해요. → 수업이 끝나면 수업 기록 / 녹화 목록에서 해당 수업을 찾아요. → ▶ 재생을 눌러 그 자리에서 확인해요. → 학부모 공유가 필요하면 관리자에게 요청하세요.</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>수업 후 자기 수업을 5분만 돌려 보면 말 속도·질문 비율이 눈에 띄게 개선됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="54" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>🔑</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>내 계정 관리 (비밀번호 · 화면 언어)</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>비밀번호를 잊었으면 관리자(운영팀)에게 재설정을 요청해요. → 임시 비밀번호를 받으면 로그인 후 바로 새 비밀번호로 바꿔요. → 화면 언어는 상단 🌐 EN / KR 버튼으로 바꿀 수 있어요. → 앱을 쓰면 얼굴·지문 로그인(패스키) 을 등록해 두는 것이 가장 편해요.</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>비밀번호를 자주 잊는다면 앱 패스키 등록을 권합니다. 얼굴만 보면 들어가져요.</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F347"/>
+  <dimension ref="A1:F424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5907,8 +6069,880 @@
       <c r="E347" s="33" t="n"/>
       <c r="F347" s="33" t="n"/>
     </row>
+    <row r="349" ht="26" customHeight="1">
+      <c r="A349" s="21" t="inlineStr">
+        <is>
+          <t>31  🔒 수업 통제 3종 (집중 · 배경 잠금 · 이탈 방지)  —  수업 중 딴짓·실수 이탈을 줄여요</t>
+        </is>
+      </c>
+      <c r="B349" s="22" t="n"/>
+      <c r="C349" s="22" t="n"/>
+      <c r="D349" s="22" t="n"/>
+      <c r="E349" s="22" t="n"/>
+      <c r="F349" s="22" t="n"/>
+    </row>
+    <row r="350" ht="42" customHeight="1">
+      <c r="A350" s="23" t="inlineStr">
+        <is>
+          <t>📖 수업에 집중할 수 있도록 교사가 켜고 끄는 통제 기능 세 가지가 생겼어요. 집중 모드는 학생이 수업 중 다른 화면으로 새는 것을 막고, 배경 잠금은 학생이 배경화면·꾸미기를 계속 바꾸는 것을 잠급니다. 이탈 방지는 학생이 실수로 뒤로 가기를 눌러 수업에서 나가는 것을 한 번 잡아 줘요.</t>
+        </is>
+      </c>
+      <c r="B350" s="24" t="n"/>
+      <c r="C350" s="24" t="n"/>
+      <c r="D350" s="24" t="n"/>
+      <c r="E350" s="24" t="n"/>
+      <c r="F350" s="24" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B351" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="30" customHeight="1">
+      <c r="A352" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B352" s="28" t="inlineStr">
+        <is>
+          <t>수업 화면 하단 독에서 ⚙️ 설정을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="30" customHeight="1">
+      <c r="A353" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B353" s="28" t="inlineStr">
+        <is>
+          <t>집중 모드를 켜면 학생 화면이 수업에 고정돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="30" customHeight="1">
+      <c r="A354" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B354" s="28" t="inlineStr">
+        <is>
+          <t>배경 잠금을 켜면 학생이 배경·얼굴 꾸미기를 바꿀 수 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="30" customHeight="1">
+      <c r="A355" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B355" s="28" t="inlineStr">
+        <is>
+          <t>이탈 방지는 켜 두면 학생이 뒤로 가기를 눌러도 정말 나갈지 한 번 물어봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="30" customHeight="1">
+      <c r="A356" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B356" s="28" t="inlineStr">
+        <is>
+          <t>수업이 끝나면 세 가지 모두 자동으로 풀립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="24" customHeight="1">
+      <c r="A357" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B357" s="30" t="inlineStr">
+        <is>
+          <t>학생이 수업 중 잠깐 끊겨도 수업은 종료되지 않아요 — 되돌아오면 그대로 이어집니다.</t>
+        </is>
+      </c>
+      <c r="C357" s="31" t="n"/>
+      <c r="D357" s="31" t="n"/>
+      <c r="E357" s="31" t="n"/>
+      <c r="F357" s="31" t="n"/>
+    </row>
+    <row r="358" ht="24" customHeight="1">
+      <c r="A358" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B358" s="30" t="inlineStr">
+        <is>
+          <t>무단 결석은 자동으로 집계돼 관리자 화면에 남아요.</t>
+        </is>
+      </c>
+      <c r="C358" s="31" t="n"/>
+      <c r="D358" s="31" t="n"/>
+      <c r="E358" s="31" t="n"/>
+      <c r="F358" s="31" t="n"/>
+    </row>
+    <row r="359" ht="24" customHeight="1">
+      <c r="A359" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B359" s="30" t="inlineStr">
+        <is>
+          <t>저학년 수업에서 특히 효과가 큽니다.</t>
+        </is>
+      </c>
+      <c r="C359" s="31" t="n"/>
+      <c r="D359" s="31" t="n"/>
+      <c r="E359" s="31" t="n"/>
+      <c r="F359" s="31" t="n"/>
+    </row>
+    <row r="360" ht="26" customHeight="1">
+      <c r="A360" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 통제 기능은 학생을 벌주는 도구가 아니라 집중을 돕는 도구입니다. 수업 시작 때 학생에게 한 번 설명해 주세요.</t>
+        </is>
+      </c>
+      <c r="B360" s="35" t="n"/>
+      <c r="C360" s="35" t="n"/>
+      <c r="D360" s="35" t="n"/>
+      <c r="E360" s="35" t="n"/>
+      <c r="F360" s="35" t="n"/>
+    </row>
+    <row r="361" ht="30" customHeight="1">
+      <c r="A361" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 산만한 학생만 골라 켜는 것보다, 첫 수업부터 기본으로 켜 두는 편이 자연스럽습니다.</t>
+        </is>
+      </c>
+      <c r="B361" s="33" t="n"/>
+      <c r="C361" s="33" t="n"/>
+      <c r="D361" s="33" t="n"/>
+      <c r="E361" s="33" t="n"/>
+      <c r="F361" s="33" t="n"/>
+    </row>
+    <row r="363" ht="26" customHeight="1">
+      <c r="A363" s="21" t="inlineStr">
+        <is>
+          <t>32  ✍️ 교재 PDF — 필기 이어가기 · 빠른 페이지 이동  —  페이지를 넘겨도 필기가 남아요</t>
+        </is>
+      </c>
+      <c r="B363" s="22" t="n"/>
+      <c r="C363" s="22" t="n"/>
+      <c r="D363" s="22" t="n"/>
+      <c r="E363" s="22" t="n"/>
+      <c r="F363" s="22" t="n"/>
+    </row>
+    <row r="364" ht="42" customHeight="1">
+      <c r="A364" s="23" t="inlineStr">
+        <is>
+          <t>📖 교재 PDF에 쓴 필기가 페이지를 넘겼다 돌아와도 그대로 남습니다. 페이지 이동도 ◀ ▶ 버튼과 페이지 번호 입력으로 빨라졌고, 오래된 기기나 회선이 느릴 때를 위한 가벼운 모드가 생겨 넘김이 부드러워졌어요.</t>
+        </is>
+      </c>
+      <c r="B364" s="24" t="n"/>
+      <c r="C364" s="24" t="n"/>
+      <c r="D364" s="24" t="n"/>
+      <c r="E364" s="24" t="n"/>
+      <c r="F364" s="24" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B365" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="30" customHeight="1">
+      <c r="A366" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B366" s="28" t="inlineStr">
+        <is>
+          <t>상단 탭에서 교재를 열고 PDF를 띄워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="30" customHeight="1">
+      <c r="A367" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B367" s="28" t="inlineStr">
+        <is>
+          <t>필기도구로 밑줄·동그라미를 그려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="30" customHeight="1">
+      <c r="A368" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B368" s="28" t="inlineStr">
+        <is>
+          <t>◀ ▶ 로 페이지를 넘기거나 페이지 번호를 직접 입력해 이동해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="30" customHeight="1">
+      <c r="A369" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B369" s="28" t="inlineStr">
+        <is>
+          <t>앞 페이지로 돌아가면 아까 쓴 필기가 그대로 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="30" customHeight="1">
+      <c r="A370" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B370" s="28" t="inlineStr">
+        <is>
+          <t>화면이 느리면 가벼운 모드를 켜세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="24" customHeight="1">
+      <c r="A371" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B371" s="30" t="inlineStr">
+        <is>
+          <t>필기는 페이지별로 따로 저장돼 섞이지 않아요.</t>
+        </is>
+      </c>
+      <c r="C371" s="31" t="n"/>
+      <c r="D371" s="31" t="n"/>
+      <c r="E371" s="31" t="n"/>
+      <c r="F371" s="31" t="n"/>
+    </row>
+    <row r="372" ht="24" customHeight="1">
+      <c r="A372" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B372" s="30" t="inlineStr">
+        <is>
+          <t>가벼운 모드는 화질을 조금 낮추는 대신 넘김이 훨씬 부드러워요.</t>
+        </is>
+      </c>
+      <c r="C372" s="31" t="n"/>
+      <c r="D372" s="31" t="n"/>
+      <c r="E372" s="31" t="n"/>
+      <c r="F372" s="31" t="n"/>
+    </row>
+    <row r="373" ht="24" customHeight="1">
+      <c r="A373" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B373" s="30" t="inlineStr">
+        <is>
+          <t>학생 화면에도 같은 페이지·같은 필기가 그대로 보여요.</t>
+        </is>
+      </c>
+      <c r="C373" s="31" t="n"/>
+      <c r="D373" s="31" t="n"/>
+      <c r="E373" s="31" t="n"/>
+      <c r="F373" s="31" t="n"/>
+    </row>
+    <row r="374" ht="30" customHeight="1">
+      <c r="A374" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 수업 전에 자주 쓸 페이지 번호를 적어 두면 이동이 빨라집니다.</t>
+        </is>
+      </c>
+      <c r="B374" s="33" t="n"/>
+      <c r="C374" s="33" t="n"/>
+      <c r="D374" s="33" t="n"/>
+      <c r="E374" s="33" t="n"/>
+      <c r="F374" s="33" t="n"/>
+    </row>
+    <row r="376" ht="26" customHeight="1">
+      <c r="A376" s="21" t="inlineStr">
+        <is>
+          <t>33  🔉 인터넷이 느릴 때 자동으로 버텨요  —  영상은 잠시 접어도 목소리는 끊기지 않게</t>
+        </is>
+      </c>
+      <c r="B376" s="22" t="n"/>
+      <c r="C376" s="22" t="n"/>
+      <c r="D376" s="22" t="n"/>
+      <c r="E376" s="22" t="n"/>
+      <c r="F376" s="22" t="n"/>
+    </row>
+    <row r="377" ht="42" customHeight="1">
+      <c r="A377" s="23" t="inlineStr">
+        <is>
+          <t>📖 회선이 나빠지면 시스템이 스스로 화질을 낮추고, 그래도 힘들면 목소리 중심(오디오 전용) 모드로 자동 전환해 수업이 끊기지 않게 버팁니다. 회선이 회복되면 영상이 다시 돌아옵니다. 필리핀 현지처럼 회선이 불안정한 환경을 염두에 둔 기능이에요.</t>
+        </is>
+      </c>
+      <c r="B377" s="24" t="n"/>
+      <c r="C377" s="24" t="n"/>
+      <c r="D377" s="24" t="n"/>
+      <c r="E377" s="24" t="n"/>
+      <c r="F377" s="24" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B378" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="30" customHeight="1">
+      <c r="A379" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B379" s="28" t="inlineStr">
+        <is>
+          <t>특별히 누를 것은 없어요 — 자동으로 동작합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="30" customHeight="1">
+      <c r="A380" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B380" s="28" t="inlineStr">
+        <is>
+          <t>화면이 흐려지거나 영상이 잠시 멈추면 목소리에 집중해 수업을 이어가세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="30" customHeight="1">
+      <c r="A381" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B381" s="28" t="inlineStr">
+        <is>
+          <t>회선이 좋아지면 영상이 저절로 돌아옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="30" customHeight="1">
+      <c r="A382" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B382" s="28" t="inlineStr">
+        <is>
+          <t>계속 불안정하면 학생에게 와이파이 가까이 이동을 안내해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="24" customHeight="1">
+      <c r="A383" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B383" s="30" t="inlineStr">
+        <is>
+          <t>목소리를 가장 마지막까지 지킵니다 — 수업은 말로 이어질 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C383" s="31" t="n"/>
+      <c r="D383" s="31" t="n"/>
+      <c r="E383" s="31" t="n"/>
+      <c r="F383" s="31" t="n"/>
+    </row>
+    <row r="384" ht="24" customHeight="1">
+      <c r="A384" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B384" s="30" t="inlineStr">
+        <is>
+          <t>잠깐 끊긴 것만으로 수업이 자동 종료되지 않아요.</t>
+        </is>
+      </c>
+      <c r="C384" s="31" t="n"/>
+      <c r="D384" s="31" t="n"/>
+      <c r="E384" s="31" t="n"/>
+      <c r="F384" s="31" t="n"/>
+    </row>
+    <row r="385" ht="24" customHeight="1">
+      <c r="A385" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B385" s="30" t="inlineStr">
+        <is>
+          <t>상대 화면이 검게 멈추면 스스로 복구를 시도합니다.</t>
+        </is>
+      </c>
+      <c r="C385" s="31" t="n"/>
+      <c r="D385" s="31" t="n"/>
+      <c r="E385" s="31" t="n"/>
+      <c r="F385" s="31" t="n"/>
+    </row>
+    <row r="386" ht="26" customHeight="1">
+      <c r="A386" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 90초 넘게 돌아오지 않으면 안내 카드가 뜹니다. 그때 학생에게 연락해 주세요.</t>
+        </is>
+      </c>
+      <c r="B386" s="35" t="n"/>
+      <c r="C386" s="35" t="n"/>
+      <c r="D386" s="35" t="n"/>
+      <c r="E386" s="35" t="n"/>
+      <c r="F386" s="35" t="n"/>
+    </row>
+    <row r="387" ht="30" customHeight="1">
+      <c r="A387" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 영상이 자주 끊기는 학생은 수업 전 장비 점검 화면을 한 번 돌려 보게 하세요.</t>
+        </is>
+      </c>
+      <c r="B387" s="33" t="n"/>
+      <c r="C387" s="33" t="n"/>
+      <c r="D387" s="33" t="n"/>
+      <c r="E387" s="33" t="n"/>
+      <c r="F387" s="33" t="n"/>
+    </row>
+    <row r="389" ht="26" customHeight="1">
+      <c r="A389" s="21" t="inlineStr">
+        <is>
+          <t>34  🧠 판단력 훈련 함께하기 (수업 중)  —  학생의 판단 과정을 수업 자료로</t>
+        </is>
+      </c>
+      <c r="B389" s="22" t="n"/>
+      <c r="C389" s="22" t="n"/>
+      <c r="D389" s="22" t="n"/>
+      <c r="E389" s="22" t="n"/>
+      <c r="F389" s="22" t="n"/>
+    </row>
+    <row r="390" ht="42" customHeight="1">
+      <c r="A390" s="23" t="inlineStr">
+        <is>
+          <t>📖 학생이 푸는 판단력 훈련을 수업에서 함께 쓰면 좋습니다. 학생이 고른 답과 그렇게 고른 이유가 그대로 남기 때문에, 단순 정오답이 아니라 왜 그렇게 생각했는지를 짚어 줄 수 있어요. 수업 중 학생의 판단이 기록되면 성장 지표에도 반영됩니다.</t>
+        </is>
+      </c>
+      <c r="B390" s="24" t="n"/>
+      <c r="C390" s="24" t="n"/>
+      <c r="D390" s="24" t="n"/>
+      <c r="E390" s="24" t="n"/>
+      <c r="F390" s="24" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B391" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="30" customHeight="1">
+      <c r="A392" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B392" s="28" t="inlineStr">
+        <is>
+          <t>수업 중 학생에게 🧠 판단력 훈련을 열게 하고 한 문제를 함께 풀어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="30" customHeight="1">
+      <c r="A393" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B393" s="28" t="inlineStr">
+        <is>
+          <t>학생이 고른 보기와 적은 이유를 소리 내어 읽게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="30" customHeight="1">
+      <c r="A394" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B394" s="28" t="inlineStr">
+        <is>
+          <t>왜 다른 보기가 덜 어울리는지 상대·말투·상황 기준으로 설명해 줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="30" customHeight="1">
+      <c r="A395" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B395" s="28" t="inlineStr">
+        <is>
+          <t>수업이 끝나면 학생 리포트에서 판단력 지수 변화를 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="24" customHeight="1">
+      <c r="A396" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B396" s="30" t="inlineStr">
+        <is>
+          <t>보기마다 부분 점수가 있어 완전 오답이 아니면 인정돼요 — 학생이 위축되지 않아요.</t>
+        </is>
+      </c>
+      <c r="C396" s="31" t="n"/>
+      <c r="D396" s="31" t="n"/>
+      <c r="E396" s="31" t="n"/>
+      <c r="F396" s="31" t="n"/>
+    </row>
+    <row r="397" ht="24" customHeight="1">
+      <c r="A397" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B397" s="30" t="inlineStr">
+        <is>
+          <t>최근 답변에 더 큰 가중치가 붙어, 최근에 좋아진 학생은 지수도 빨리 올라가요.</t>
+        </is>
+      </c>
+      <c r="C397" s="31" t="n"/>
+      <c r="D397" s="31" t="n"/>
+      <c r="E397" s="31" t="n"/>
+      <c r="F397" s="31" t="n"/>
+    </row>
+    <row r="398" ht="24" customHeight="1">
+      <c r="A398" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B398" s="30" t="inlineStr">
+        <is>
+          <t>틀린 뒤 다음 문제를 잘 푸는 회복형 학생이 따로 잡혀요.</t>
+        </is>
+      </c>
+      <c r="C398" s="31" t="n"/>
+      <c r="D398" s="31" t="n"/>
+      <c r="E398" s="31" t="n"/>
+      <c r="F398" s="31" t="n"/>
+    </row>
+    <row r="399" ht="30" customHeight="1">
+      <c r="A399" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · “왜 그렇게 생각했어요?”를 영어로 묻고 한국어로 답하게 해도 좋습니다. 판단 과정이 먼저입니다.</t>
+        </is>
+      </c>
+      <c r="B399" s="33" t="n"/>
+      <c r="C399" s="33" t="n"/>
+      <c r="D399" s="33" t="n"/>
+      <c r="E399" s="33" t="n"/>
+      <c r="F399" s="33" t="n"/>
+    </row>
+    <row r="401" ht="26" customHeight="1">
+      <c r="A401" s="21" t="inlineStr">
+        <is>
+          <t>35  🎥 지난 수업 녹화 다시보기  —  녹화된 수업을 그 자리에서 재생</t>
+        </is>
+      </c>
+      <c r="B401" s="22" t="n"/>
+      <c r="C401" s="22" t="n"/>
+      <c r="D401" s="22" t="n"/>
+      <c r="E401" s="22" t="n"/>
+      <c r="F401" s="22" t="n"/>
+    </row>
+    <row r="402" ht="42" customHeight="1">
+      <c r="A402" s="23" t="inlineStr">
+        <is>
+          <t>📖 수업 중 REC 로 녹화한 영상을 나중에 관리 화면에서 바로 재생할 수 있습니다. 내려받지 않아도 클릭 한 번으로 재생되고, 다시 로그인하라는 화면이 뜨던 문제도 해결했어요.</t>
+        </is>
+      </c>
+      <c r="B402" s="24" t="n"/>
+      <c r="C402" s="24" t="n"/>
+      <c r="D402" s="24" t="n"/>
+      <c r="E402" s="24" t="n"/>
+      <c r="F402" s="24" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B403" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="30" customHeight="1">
+      <c r="A404" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B404" s="28" t="inlineStr">
+        <is>
+          <t>수업 중 상단의 REC 를 눌러 녹화해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="30" customHeight="1">
+      <c r="A405" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B405" s="28" t="inlineStr">
+        <is>
+          <t>수업이 끝나면 수업 기록 / 녹화 목록에서 해당 수업을 찾아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="30" customHeight="1">
+      <c r="A406" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B406" s="28" t="inlineStr">
+        <is>
+          <t>▶ 재생을 눌러 그 자리에서 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="30" customHeight="1">
+      <c r="A407" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B407" s="28" t="inlineStr">
+        <is>
+          <t>학부모 공유가 필요하면 관리자에게 요청하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="24" customHeight="1">
+      <c r="A408" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B408" s="30" t="inlineStr">
+        <is>
+          <t>재생 중 로그인 화면으로 튕기지 않아요.</t>
+        </is>
+      </c>
+      <c r="C408" s="31" t="n"/>
+      <c r="D408" s="31" t="n"/>
+      <c r="E408" s="31" t="n"/>
+      <c r="F408" s="31" t="n"/>
+    </row>
+    <row r="409" ht="24" customHeight="1">
+      <c r="A409" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B409" s="30" t="inlineStr">
+        <is>
+          <t>녹화 파일은 서버에 보관되며 용량 정책에 따라 정리됩니다.</t>
+        </is>
+      </c>
+      <c r="C409" s="31" t="n"/>
+      <c r="D409" s="31" t="n"/>
+      <c r="E409" s="31" t="n"/>
+      <c r="F409" s="31" t="n"/>
+    </row>
+    <row r="410" ht="24" customHeight="1">
+      <c r="A410" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B410" s="30" t="inlineStr">
+        <is>
+          <t>학생 얼굴이 담기므로 외부 공유는 금지입니다.</t>
+        </is>
+      </c>
+      <c r="C410" s="31" t="n"/>
+      <c r="D410" s="31" t="n"/>
+      <c r="E410" s="31" t="n"/>
+      <c r="F410" s="31" t="n"/>
+    </row>
+    <row r="411" ht="26" customHeight="1">
+      <c r="A411" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 녹화는 학생·학부모 동의가 있는 경우에만 사용하세요.</t>
+        </is>
+      </c>
+      <c r="B411" s="35" t="n"/>
+      <c r="C411" s="35" t="n"/>
+      <c r="D411" s="35" t="n"/>
+      <c r="E411" s="35" t="n"/>
+      <c r="F411" s="35" t="n"/>
+    </row>
+    <row r="412" ht="30" customHeight="1">
+      <c r="A412" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 수업 후 자기 수업을 5분만 돌려 보면 말 속도·질문 비율이 눈에 띄게 개선됩니다.</t>
+        </is>
+      </c>
+      <c r="B412" s="33" t="n"/>
+      <c r="C412" s="33" t="n"/>
+      <c r="D412" s="33" t="n"/>
+      <c r="E412" s="33" t="n"/>
+      <c r="F412" s="33" t="n"/>
+    </row>
+    <row r="414" ht="26" customHeight="1">
+      <c r="A414" s="21" t="inlineStr">
+        <is>
+          <t>36  🔑 내 계정 관리 (비밀번호 · 화면 언어)  —  비밀번호를 잊었을 때 · 영어 화면 설정</t>
+        </is>
+      </c>
+      <c r="B414" s="22" t="n"/>
+      <c r="C414" s="22" t="n"/>
+      <c r="D414" s="22" t="n"/>
+      <c r="E414" s="22" t="n"/>
+      <c r="F414" s="22" t="n"/>
+    </row>
+    <row r="415" ht="42" customHeight="1">
+      <c r="A415" s="23" t="inlineStr">
+        <is>
+          <t>📖 비밀번호를 잊었을 때 관리자에게 요청하면 바로 재설정해 줍니다. 또 강사 계정은 화면이 항상 영어로 뜨도록 바뀌어서, 한국어 화면 때문에 메뉴를 못 찾는 일이 없어졌어요.</t>
+        </is>
+      </c>
+      <c r="B415" s="24" t="n"/>
+      <c r="C415" s="24" t="n"/>
+      <c r="D415" s="24" t="n"/>
+      <c r="E415" s="24" t="n"/>
+      <c r="F415" s="24" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B416" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="30" customHeight="1">
+      <c r="A417" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B417" s="28" t="inlineStr">
+        <is>
+          <t>비밀번호를 잊었으면 관리자(운영팀)에게 재설정을 요청해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="30" customHeight="1">
+      <c r="A418" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B418" s="28" t="inlineStr">
+        <is>
+          <t>임시 비밀번호를 받으면 로그인 후 바로 새 비밀번호로 바꿔요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="30" customHeight="1">
+      <c r="A419" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B419" s="28" t="inlineStr">
+        <is>
+          <t>화면 언어는 상단 🌐 EN / KR 버튼으로 바꿀 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="30" customHeight="1">
+      <c r="A420" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B420" s="28" t="inlineStr">
+        <is>
+          <t>앱을 쓰면 얼굴·지문 로그인(패스키) 을 등록해 두는 것이 가장 편해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="24" customHeight="1">
+      <c r="A421" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B421" s="30" t="inlineStr">
+        <is>
+          <t>강사 계정은 기본이 영어 화면입니다.</t>
+        </is>
+      </c>
+      <c r="C421" s="31" t="n"/>
+      <c r="D421" s="31" t="n"/>
+      <c r="E421" s="31" t="n"/>
+      <c r="F421" s="31" t="n"/>
+    </row>
+    <row r="422" ht="24" customHeight="1">
+      <c r="A422" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B422" s="30" t="inlineStr">
+        <is>
+          <t>직접 고른 언어는 내 계정에만 저장돼요.</t>
+        </is>
+      </c>
+      <c r="C422" s="31" t="n"/>
+      <c r="D422" s="31" t="n"/>
+      <c r="E422" s="31" t="n"/>
+      <c r="F422" s="31" t="n"/>
+    </row>
+    <row r="423" ht="24" customHeight="1">
+      <c r="A423" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B423" s="30" t="inlineStr">
+        <is>
+          <t>임시 비밀번호는 반드시 바꿔서 쓰세요.</t>
+        </is>
+      </c>
+      <c r="C423" s="31" t="n"/>
+      <c r="D423" s="31" t="n"/>
+      <c r="E423" s="31" t="n"/>
+      <c r="F423" s="31" t="n"/>
+    </row>
+    <row r="424" ht="30" customHeight="1">
+      <c r="A424" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 비밀번호를 자주 잊는다면 앱 패스키 등록을 권합니다. 얼굴만 보면 들어가져요.</t>
+        </is>
+      </c>
+      <c r="B424" s="33" t="n"/>
+      <c r="C424" s="33" t="n"/>
+      <c r="D424" s="33" t="n"/>
+      <c r="E424" s="33" t="n"/>
+      <c r="F424" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="317">
+  <mergeCells count="388">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B276:F276"/>
@@ -5926,20 +6960,28 @@
     <mergeCell ref="A257:F257"/>
     <mergeCell ref="B158:F158"/>
     <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A349:F349"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B369:F369"/>
+    <mergeCell ref="B418:F418"/>
     <mergeCell ref="A315:F315"/>
+    <mergeCell ref="B356:F356"/>
     <mergeCell ref="B160:F160"/>
+    <mergeCell ref="B368:F368"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B306:F306"/>
     <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B420:F420"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B370:F370"/>
     <mergeCell ref="A267:F267"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="A269:F269"/>
     <mergeCell ref="B293:F293"/>
     <mergeCell ref="B322:F322"/>
+    <mergeCell ref="A377:F377"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="B82:F82"/>
@@ -5952,11 +6994,14 @@
     <mergeCell ref="B254:F254"/>
     <mergeCell ref="B319:F319"/>
     <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B383:F383"/>
     <mergeCell ref="A346:F346"/>
     <mergeCell ref="A90:F90"/>
     <mergeCell ref="A217:F217"/>
     <mergeCell ref="B141:F141"/>
     <mergeCell ref="B159:F159"/>
+    <mergeCell ref="A415:F415"/>
+    <mergeCell ref="A390:F390"/>
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="B272:F272"/>
     <mergeCell ref="B136:F136"/>
@@ -5964,6 +7009,7 @@
     <mergeCell ref="B225:F225"/>
     <mergeCell ref="B274:F274"/>
     <mergeCell ref="B243:F243"/>
+    <mergeCell ref="B373:F373"/>
     <mergeCell ref="A270:F270"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A207:F207"/>
@@ -5971,17 +7017,21 @@
     <mergeCell ref="B154:F154"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A363:F363"/>
     <mergeCell ref="B156:F156"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B155:F155"/>
     <mergeCell ref="B264:F264"/>
     <mergeCell ref="B320:F320"/>
+    <mergeCell ref="B391:F391"/>
+    <mergeCell ref="B385:F385"/>
     <mergeCell ref="A302:F302"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="B262:F262"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B101:F101"/>
     <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A389:F389"/>
     <mergeCell ref="A327:F327"/>
     <mergeCell ref="B182:F182"/>
     <mergeCell ref="A220:F220"/>
@@ -5992,21 +7042,28 @@
     <mergeCell ref="B275:F275"/>
     <mergeCell ref="B340:F340"/>
     <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B404:F404"/>
     <mergeCell ref="B81:F81"/>
     <mergeCell ref="B252:F252"/>
+    <mergeCell ref="B366:F366"/>
     <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B381:F381"/>
     <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A386:F386"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="B157:F157"/>
     <mergeCell ref="B234:F234"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B172:F172"/>
+    <mergeCell ref="B392:F392"/>
     <mergeCell ref="A289:F289"/>
     <mergeCell ref="B186:F186"/>
     <mergeCell ref="B288:F288"/>
     <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B394:F394"/>
     <mergeCell ref="A291:F291"/>
     <mergeCell ref="B265:F265"/>
+    <mergeCell ref="A399:F399"/>
     <mergeCell ref="A305:F305"/>
     <mergeCell ref="A292:F292"/>
     <mergeCell ref="B54:F54"/>
@@ -6016,10 +7073,15 @@
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B341:F341"/>
     <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B405:F405"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="B171:F171"/>
+    <mergeCell ref="B407:F407"/>
     <mergeCell ref="A176:F176"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A412:F412"/>
+    <mergeCell ref="A387:F387"/>
+    <mergeCell ref="B359:F359"/>
     <mergeCell ref="B204:F204"/>
     <mergeCell ref="B296:F296"/>
     <mergeCell ref="B173:F173"/>
@@ -6036,6 +7098,7 @@
     <mergeCell ref="A229:F229"/>
     <mergeCell ref="B255:F255"/>
     <mergeCell ref="B226:F226"/>
+    <mergeCell ref="A402:F402"/>
     <mergeCell ref="B192:F192"/>
     <mergeCell ref="B284:F284"/>
     <mergeCell ref="B222:F222"/>
@@ -6046,17 +7109,20 @@
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B286:F286"/>
     <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A364:F364"/>
     <mergeCell ref="A219:F219"/>
     <mergeCell ref="B297:F297"/>
     <mergeCell ref="B235:F235"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="B103:F103"/>
     <mergeCell ref="B205:F205"/>
+    <mergeCell ref="B403:F403"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B169:F169"/>
     <mergeCell ref="A187:F187"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B365:F365"/>
     <mergeCell ref="A118:F118"/>
     <mergeCell ref="A189:F189"/>
     <mergeCell ref="B71:F71"/>
@@ -6070,6 +7136,7 @@
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="B231:F231"/>
     <mergeCell ref="B287:F287"/>
+    <mergeCell ref="B358:F358"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B84:F84"/>
     <mergeCell ref="A24:F24"/>
@@ -6079,22 +7146,30 @@
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B384:F384"/>
+    <mergeCell ref="B378:F378"/>
+    <mergeCell ref="A360:F360"/>
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="B242:F242"/>
     <mergeCell ref="A335:F335"/>
     <mergeCell ref="A151:F151"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A259:F259"/>
+    <mergeCell ref="A424:F424"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A240:F240"/>
     <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A411:F411"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="B333:F333"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B308:F308"/>
     <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B422:F422"/>
+    <mergeCell ref="B397:F397"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B372:F372"/>
     <mergeCell ref="B310:F310"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A79:F79"/>
@@ -6109,7 +7184,9 @@
     <mergeCell ref="B152:F152"/>
     <mergeCell ref="B323:F323"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A374:F374"/>
     <mergeCell ref="B244:F244"/>
+    <mergeCell ref="A361:F361"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="A140:F140"/>
@@ -6119,15 +7196,19 @@
     <mergeCell ref="B147:F147"/>
     <mergeCell ref="B245:F245"/>
     <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A350:F350"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B334:F334"/>
     <mergeCell ref="B309:F309"/>
     <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B380:F380"/>
     <mergeCell ref="A316:F316"/>
     <mergeCell ref="B100:F100"/>
     <mergeCell ref="B311:F311"/>
     <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B382:F382"/>
+    <mergeCell ref="A376:F376"/>
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="A209:F209"/>
     <mergeCell ref="B29:F29"/>
@@ -6136,11 +7217,13 @@
     <mergeCell ref="B95:F95"/>
     <mergeCell ref="B266:F266"/>
     <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B393:F393"/>
     <mergeCell ref="B331:F331"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B330:F330"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B395:F395"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="B261:F261"/>
     <mergeCell ref="B184:F184"/>
@@ -6150,11 +7233,15 @@
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B166:F166"/>
+    <mergeCell ref="B408:F408"/>
     <mergeCell ref="A161:F161"/>
+    <mergeCell ref="B352:F352"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B423:F423"/>
     <mergeCell ref="B168:F168"/>
+    <mergeCell ref="B410:F410"/>
     <mergeCell ref="B143:F143"/>
     <mergeCell ref="B281:F281"/>
     <mergeCell ref="B20:F20"/>
@@ -6163,16 +7250,22 @@
     <mergeCell ref="A237:F237"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A277:F277"/>
+    <mergeCell ref="B355:F355"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="B121:F121"/>
+    <mergeCell ref="B357:F357"/>
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B167:F167"/>
     <mergeCell ref="B332:F332"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B421:F421"/>
     <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B396:F396"/>
     <mergeCell ref="B175:F175"/>
     <mergeCell ref="A230:F230"/>
+    <mergeCell ref="A401:F401"/>
+    <mergeCell ref="B398:F398"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A304:F304"/>
     <mergeCell ref="B124:F124"/>
@@ -6185,25 +7278,32 @@
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B351:F351"/>
     <mergeCell ref="B345:F345"/>
     <mergeCell ref="A164:F164"/>
+    <mergeCell ref="B416:F416"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="B295:F295"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B282:F282"/>
     <mergeCell ref="A179:F179"/>
+    <mergeCell ref="B409:F409"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A414:F414"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A324:F324"/>
     <mergeCell ref="A180:F180"/>
     <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B371:F371"/>
     <mergeCell ref="A93:F93"/>
+    <mergeCell ref="B379:F379"/>
     <mergeCell ref="A328:F328"/>
     <mergeCell ref="B300:F300"/>
     <mergeCell ref="B183:F183"/>
     <mergeCell ref="B201:F201"/>
+    <mergeCell ref="B406:F406"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B212:F212"/>
     <mergeCell ref="B206:F206"/>
@@ -6213,14 +7313,19 @@
     <mergeCell ref="A247:F247"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A312:F312"/>
+    <mergeCell ref="B353:F353"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B417:F417"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B196:F196"/>
+    <mergeCell ref="B367:F367"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B283:F283"/>
+    <mergeCell ref="B354:F354"/>
+    <mergeCell ref="B419:F419"/>
     <mergeCell ref="B298:F298"/>
     <mergeCell ref="B285:F285"/>
     <mergeCell ref="A325:F325"/>
